--- a/loan_approval_input.xlsx
+++ b/loan_approval_input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ecl.lab\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77ED1E97-DDFD-40C6-9A4E-2916660FA626}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD7DBF9E-B9A0-46E4-ADC4-56FABD25B498}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,20 @@
     <sheet name="Rules" sheetId="2" r:id="rId2"/>
     <sheet name="README" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -48,196 +61,196 @@
     <t>Employment_Years</t>
   </si>
   <si>
+    <t>Approved</t>
+  </si>
+  <si>
+    <t>Rohan Mehta</t>
+  </si>
+  <si>
+    <t>Rejected</t>
+  </si>
+  <si>
+    <t>Ananya Rao</t>
+  </si>
+  <si>
+    <t>Karan Joshi</t>
+  </si>
+  <si>
+    <t>Meera Nair</t>
+  </si>
+  <si>
+    <t>Siddharth Gupta</t>
+  </si>
+  <si>
+    <t>Pooja Bhat</t>
+  </si>
+  <si>
+    <t>Aditya Kapoor</t>
+  </si>
+  <si>
+    <t>Ishita Menon</t>
+  </si>
+  <si>
+    <t>Manish Tiwari</t>
+  </si>
+  <si>
+    <t>Kavya Shetty</t>
+  </si>
+  <si>
+    <t>Tanvi Choudhary</t>
+  </si>
+  <si>
+    <t>Parameter</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Meaning</t>
+  </si>
+  <si>
+    <t>Min_Age</t>
+  </si>
+  <si>
+    <t>Applicant must be at least this old</t>
+  </si>
+  <si>
+    <t>Min_Annual_Income</t>
+  </si>
+  <si>
+    <t>Minimum annual income (INR)</t>
+  </si>
+  <si>
+    <t>Min_Credit_Score</t>
+  </si>
+  <si>
+    <t>Minimum credit score</t>
+  </si>
+  <si>
+    <t>Min_Employment_Years</t>
+  </si>
+  <si>
+    <t>Minimum years of employment</t>
+  </si>
+  <si>
+    <t>Max_Loan_to_Income</t>
+  </si>
+  <si>
+    <t>Loan_Amount / Annual_Income must not exceed this</t>
+  </si>
+  <si>
+    <t>Max_Debt_to_Income</t>
+  </si>
+  <si>
+    <t>Existing_Debt / Annual_Income must not exceed this</t>
+  </si>
+  <si>
+    <t>LOAN APPROVAL - INPUT FILE (all numbers here are fictional)</t>
+  </si>
+  <si>
+    <t>Yellow cells are inputs. Edit any of them (income, credit score, rules, historical decision...), save, then re-run the notebook.</t>
+  </si>
+  <si>
+    <t>The output file (loan_approval_output.xlsx) is rebuilt from this file, so every change appears there.</t>
+  </si>
+  <si>
+    <t>Applicants sheet: keep the header names and keep Historical_Decision as 'Approved' or 'Rejected'. You may add/remove applicant rows.</t>
+  </si>
+  <si>
+    <t>Rules sheet: thresholds used by the TRADITIONAL (rule-based) program. Keep the Parameter names unchanged.</t>
+  </si>
+  <si>
+    <t>Historical_Decision is the 'answer' the ML model learns from.</t>
+  </si>
+  <si>
+    <t>C001</t>
+  </si>
+  <si>
+    <t>C002</t>
+  </si>
+  <si>
+    <t>C003</t>
+  </si>
+  <si>
+    <t>C004</t>
+  </si>
+  <si>
+    <t>C005</t>
+  </si>
+  <si>
+    <t>C006</t>
+  </si>
+  <si>
+    <t>C007</t>
+  </si>
+  <si>
+    <t>C008</t>
+  </si>
+  <si>
+    <t>C009</t>
+  </si>
+  <si>
+    <t>C010</t>
+  </si>
+  <si>
+    <t>C011</t>
+  </si>
+  <si>
+    <t>C012</t>
+  </si>
+  <si>
+    <t>C013</t>
+  </si>
+  <si>
+    <t>C014</t>
+  </si>
+  <si>
+    <t>C015</t>
+  </si>
+  <si>
+    <t>C016</t>
+  </si>
+  <si>
+    <t>C017</t>
+  </si>
+  <si>
+    <t>C018</t>
+  </si>
+  <si>
+    <t>C019</t>
+  </si>
+  <si>
+    <t>C020</t>
+  </si>
+  <si>
+    <t>Aayush Dev</t>
+  </si>
+  <si>
+    <t>Sara Khan</t>
+  </si>
+  <si>
+    <t>Vishal Singh</t>
+  </si>
+  <si>
+    <t>Sneha K.C</t>
+  </si>
+  <si>
+    <t>Divyanka Kulkarni</t>
+  </si>
+  <si>
+    <t>Jayalakshmi Verma</t>
+  </si>
+  <si>
+    <t>Huzaifa Desai</t>
+  </si>
+  <si>
+    <t>Aaron Pir</t>
+  </si>
+  <si>
+    <t>Melania Gomes</t>
+  </si>
+  <si>
     <t>Historical_Decision</t>
-  </si>
-  <si>
-    <t>A001</t>
-  </si>
-  <si>
-    <t>Aarav Sharma</t>
-  </si>
-  <si>
-    <t>Approved</t>
-  </si>
-  <si>
-    <t>A002</t>
-  </si>
-  <si>
-    <t>Priya Patel</t>
-  </si>
-  <si>
-    <t>A003</t>
-  </si>
-  <si>
-    <t>Rohan Mehta</t>
-  </si>
-  <si>
-    <t>Rejected</t>
-  </si>
-  <si>
-    <t>A004</t>
-  </si>
-  <si>
-    <t>Sneha Iyer</t>
-  </si>
-  <si>
-    <t>A005</t>
-  </si>
-  <si>
-    <t>Vikram Singh</t>
-  </si>
-  <si>
-    <t>A006</t>
-  </si>
-  <si>
-    <t>Ananya Rao</t>
-  </si>
-  <si>
-    <t>A007</t>
-  </si>
-  <si>
-    <t>Karan Joshi</t>
-  </si>
-  <si>
-    <t>A008</t>
-  </si>
-  <si>
-    <t>Meera Nair</t>
-  </si>
-  <si>
-    <t>A009</t>
-  </si>
-  <si>
-    <t>Arjun Reddy</t>
-  </si>
-  <si>
-    <t>A010</t>
-  </si>
-  <si>
-    <t>Divya Kulkarni</t>
-  </si>
-  <si>
-    <t>A011</t>
-  </si>
-  <si>
-    <t>Siddharth Gupta</t>
-  </si>
-  <si>
-    <t>A012</t>
-  </si>
-  <si>
-    <t>Neha Verma</t>
-  </si>
-  <si>
-    <t>A013</t>
-  </si>
-  <si>
-    <t>Rahul Desai</t>
-  </si>
-  <si>
-    <t>A014</t>
-  </si>
-  <si>
-    <t>Pooja Bhat</t>
-  </si>
-  <si>
-    <t>A015</t>
-  </si>
-  <si>
-    <t>Aditya Kapoor</t>
-  </si>
-  <si>
-    <t>A016</t>
-  </si>
-  <si>
-    <t>Ishita Menon</t>
-  </si>
-  <si>
-    <t>A017</t>
-  </si>
-  <si>
-    <t>Manish Tiwari</t>
-  </si>
-  <si>
-    <t>A018</t>
-  </si>
-  <si>
-    <t>Kavya Shetty</t>
-  </si>
-  <si>
-    <t>A019</t>
-  </si>
-  <si>
-    <t>Nikhil Pandey</t>
-  </si>
-  <si>
-    <t>A020</t>
-  </si>
-  <si>
-    <t>Tanvi Choudhary</t>
-  </si>
-  <si>
-    <t>Parameter</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Meaning</t>
-  </si>
-  <si>
-    <t>Min_Age</t>
-  </si>
-  <si>
-    <t>Applicant must be at least this old</t>
-  </si>
-  <si>
-    <t>Min_Annual_Income</t>
-  </si>
-  <si>
-    <t>Minimum annual income (INR)</t>
-  </si>
-  <si>
-    <t>Min_Credit_Score</t>
-  </si>
-  <si>
-    <t>Minimum credit score</t>
-  </si>
-  <si>
-    <t>Min_Employment_Years</t>
-  </si>
-  <si>
-    <t>Minimum years of employment</t>
-  </si>
-  <si>
-    <t>Max_Loan_to_Income</t>
-  </si>
-  <si>
-    <t>Loan_Amount / Annual_Income must not exceed this</t>
-  </si>
-  <si>
-    <t>Max_Debt_to_Income</t>
-  </si>
-  <si>
-    <t>Existing_Debt / Annual_Income must not exceed this</t>
-  </si>
-  <si>
-    <t>LOAN APPROVAL - INPUT FILE (all numbers here are fictional)</t>
-  </si>
-  <si>
-    <t>Yellow cells are inputs. Edit any of them (income, credit score, rules, historical decision...), save, then re-run the notebook.</t>
-  </si>
-  <si>
-    <t>The output file (loan_approval_output.xlsx) is rebuilt from this file, so every change appears there.</t>
-  </si>
-  <si>
-    <t>Applicants sheet: keep the header names and keep Historical_Decision as 'Approved' or 'Rejected'. You may add/remove applicant rows.</t>
-  </si>
-  <si>
-    <t>Rules sheet: thresholds used by the TRADITIONAL (rule-based) program. Keep the Parameter names unchanged.</t>
-  </si>
-  <si>
-    <t>Historical_Decision is the 'answer' the ML model learns from.</t>
   </si>
 </sst>
 </file>
@@ -662,587 +675,587 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>8</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>10</v>
+        <v>62</v>
       </c>
       <c r="C2" s="3">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D2" s="4">
-        <v>1050000</v>
+        <v>797379</v>
       </c>
       <c r="E2" s="3">
-        <v>750</v>
+        <v>690</v>
       </c>
       <c r="F2" s="4">
         <v>300000</v>
       </c>
       <c r="G2" s="4">
-        <v>50000</v>
+        <v>240711</v>
       </c>
       <c r="H2" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="C3" s="3">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="D3" s="4">
-        <v>1200000</v>
+        <v>1126776</v>
       </c>
       <c r="E3" s="3">
-        <v>780</v>
+        <v>701</v>
       </c>
       <c r="F3" s="4">
         <v>800000</v>
       </c>
       <c r="G3" s="4">
-        <v>100000</v>
+        <v>147972</v>
       </c>
       <c r="H3" s="3">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C4" s="3">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D4" s="4">
-        <v>3500000</v>
+        <v>956357</v>
       </c>
       <c r="E4" s="3">
-        <v>610</v>
+        <v>667</v>
       </c>
       <c r="F4" s="4">
         <v>500000</v>
       </c>
       <c r="G4" s="4">
-        <v>80000</v>
+        <v>86508</v>
       </c>
       <c r="H4" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="C5" s="3">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D5" s="4">
-        <v>1500000</v>
+        <v>874183</v>
       </c>
       <c r="E5" s="3">
-        <v>800</v>
+        <v>693</v>
       </c>
       <c r="F5" s="4">
         <v>2500000</v>
       </c>
       <c r="G5" s="4">
-        <v>200000</v>
+        <v>218560</v>
       </c>
       <c r="H5" s="3">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="C6" s="3">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D6" s="4">
-        <v>600000</v>
+        <v>1256699</v>
       </c>
       <c r="E6" s="3">
-        <v>690</v>
+        <v>675</v>
       </c>
       <c r="F6" s="4">
         <v>1800000</v>
       </c>
       <c r="G6" s="4">
-        <v>150000</v>
+        <v>128931</v>
       </c>
       <c r="H6" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="C7" s="3">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="D7" s="4">
-        <v>450000</v>
+        <v>1423525</v>
       </c>
       <c r="E7" s="3">
-        <v>680</v>
+        <v>709</v>
       </c>
       <c r="F7" s="4">
         <v>1500000</v>
       </c>
       <c r="G7" s="4">
-        <v>100000</v>
+        <v>338883</v>
       </c>
       <c r="H7" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="C8" s="3">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D8" s="4">
-        <v>1900000</v>
+        <v>1682546</v>
       </c>
       <c r="E8" s="3">
-        <v>580</v>
+        <v>652</v>
       </c>
       <c r="F8" s="4">
         <v>700000</v>
       </c>
       <c r="G8" s="4">
-        <v>300000</v>
+        <v>419150</v>
       </c>
       <c r="H8" s="3">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="C9" s="3">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D9" s="4">
-        <v>720000</v>
+        <v>1320492</v>
       </c>
       <c r="E9" s="3">
-        <v>720</v>
+        <v>729</v>
       </c>
       <c r="F9" s="4">
         <v>2000000</v>
       </c>
       <c r="G9" s="4">
-        <v>90000</v>
+        <v>72928</v>
       </c>
       <c r="H9" s="3">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="C10" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D10" s="4">
-        <v>285000</v>
+        <v>965047</v>
       </c>
       <c r="E10" s="3">
-        <v>640</v>
+        <v>674</v>
       </c>
       <c r="F10" s="4">
         <v>400000</v>
       </c>
       <c r="G10" s="4">
-        <v>20000</v>
+        <v>109065</v>
       </c>
       <c r="H10" s="3">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="C11" s="3">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D11" s="4">
-        <v>1000000</v>
+        <v>1427517</v>
       </c>
       <c r="E11" s="3">
-        <v>760</v>
+        <v>726</v>
       </c>
       <c r="F11" s="4">
         <v>3000000</v>
       </c>
       <c r="G11" s="4">
-        <v>400000</v>
+        <v>164322</v>
       </c>
       <c r="H11" s="3">
         <v>9</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="C12" s="3">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="D12" s="4">
-        <v>550000</v>
+        <v>1057549</v>
       </c>
       <c r="E12" s="3">
-        <v>720</v>
+        <v>666</v>
       </c>
       <c r="F12" s="4">
         <v>3500000</v>
       </c>
       <c r="G12" s="4">
-        <v>120000</v>
+        <v>461895</v>
       </c>
       <c r="H12" s="3">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="C13" s="3">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="D13" s="4">
-        <v>780000</v>
+        <v>1546198</v>
       </c>
       <c r="E13" s="3">
-        <v>668</v>
+        <v>679</v>
       </c>
       <c r="F13" s="4">
         <v>1200000</v>
       </c>
       <c r="G13" s="4">
-        <v>450000</v>
+        <v>345990</v>
       </c>
       <c r="H13" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="C14" s="3">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="D14" s="4">
-        <v>800000</v>
+        <v>730557</v>
       </c>
       <c r="E14" s="3">
-        <v>790</v>
+        <v>683</v>
       </c>
       <c r="F14" s="4">
         <v>4000000</v>
       </c>
       <c r="G14" s="4">
-        <v>500000</v>
+        <v>227828</v>
       </c>
       <c r="H14" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="C15" s="3">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="D15" s="4">
-        <v>500000</v>
+        <v>719017</v>
       </c>
       <c r="E15" s="3">
-        <v>695</v>
+        <v>711</v>
       </c>
       <c r="F15" s="4">
         <v>900000</v>
       </c>
       <c r="G15" s="4">
-        <v>60000</v>
+        <v>394912</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="C16" s="3">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D16" s="4">
-        <v>950000</v>
+        <v>1088398</v>
       </c>
       <c r="E16" s="3">
-        <v>630</v>
+        <v>652</v>
       </c>
       <c r="F16" s="4">
         <v>1000000</v>
       </c>
       <c r="G16" s="4">
-        <v>100000</v>
+        <v>135410</v>
       </c>
       <c r="H16" s="3">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="C17" s="3">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D17" s="4">
-        <v>400000</v>
+        <v>956757</v>
       </c>
       <c r="E17" s="3">
-        <v>720</v>
+        <v>676</v>
       </c>
       <c r="F17" s="4">
         <v>600000</v>
       </c>
       <c r="G17" s="4">
-        <v>30000</v>
+        <v>236463</v>
       </c>
       <c r="H17" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="C18" s="3">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D18" s="4">
-        <v>650000</v>
+        <v>1645719</v>
       </c>
       <c r="E18" s="3">
-        <v>670</v>
+        <v>737</v>
       </c>
       <c r="F18" s="4">
         <v>2200000</v>
       </c>
       <c r="G18" s="4">
-        <v>200000</v>
+        <v>67589</v>
       </c>
       <c r="H18" s="3">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="C19" s="3">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="D19" s="4">
-        <v>1350000</v>
+        <v>1209500</v>
       </c>
       <c r="E19" s="3">
-        <v>740</v>
+        <v>677</v>
       </c>
       <c r="F19" s="4">
         <v>1500000</v>
       </c>
       <c r="G19" s="4">
-        <v>150000</v>
+        <v>389805</v>
       </c>
       <c r="H19" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="C20" s="3">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="D20" s="4">
-        <v>320000</v>
+        <v>1149436</v>
       </c>
       <c r="E20" s="3">
-        <v>660</v>
+        <v>700</v>
       </c>
       <c r="F20" s="4">
         <v>1600000</v>
       </c>
       <c r="G20" s="4">
-        <v>50000</v>
+        <v>252694</v>
       </c>
       <c r="H20" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="C21" s="3">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="D21" s="4">
-        <v>880000</v>
+        <v>1006393</v>
       </c>
       <c r="E21" s="3">
-        <v>700</v>
+        <v>727</v>
       </c>
       <c r="F21" s="4">
         <v>2600000</v>
       </c>
       <c r="G21" s="4">
-        <v>250000</v>
+        <v>182382</v>
       </c>
       <c r="H21" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1262,79 +1275,79 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="B2" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>55</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>500000</v>
+        <v>700000</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="B4" s="3">
         <v>650</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="B5" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>61</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="B6" s="3">
         <v>4</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="B7" s="3">
         <v>0.5</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>65</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1352,32 +1365,32 @@
   <sheetData>
     <row r="1" spans="1:1" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>66</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>70</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
